--- a/output/pdf_financials_xlsx/MAR.UN.xlsx
+++ b/output/pdf_financials_xlsx/MAR.UN.xlsx
@@ -1579,22 +1579,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.471975</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.217618</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.424511</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.765615</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>4.23825</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>4.323498</v>
       </c>
     </row>
     <row r="35">
@@ -1629,22 +1629,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.471975</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.217618</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.424511</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.765615</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>4.23825</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>4.323498</v>
       </c>
     </row>
     <row r="37">
@@ -1929,22 +1929,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.471975</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.325712</v>
+        <v>0.108094</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.611286</v>
+        <v>0.186775</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.09692</v>
+        <v>0.331305</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.557902</v>
+        <v>0.319652</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.631371</v>
+        <v>0.307873</v>
       </c>
     </row>
     <row r="49">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
